--- a/data-manipulation-scripts/sheets-cleanup/sheets/PRISONEIRO COROA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/PRISONEIRO COROA.xlsx
@@ -31,7 +31,7 @@
     <t>7893986225122</t>
   </si>
   <si>
-    <t>PRISOINEIRO COROA PECA+ SUZUKI YES/ KATANA/ INTRUDER 2TRAVA 4 PARAFUSO 4PORCA</t>
+    <t>JOGO PRISOINEIRO COROA PECA+ SUZUKI YES/ KATANA/ INTRUDER 2TRAVA 4 PARAFUSO 4PORCA</t>
   </si>
 </sst>
 </file>
@@ -360,7 +360,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4">
-        <v>34.0</v>
+        <v>7.0</v>
       </c>
       <c r="D2" s="4">
         <v>25.0</v>
